--- a/artfynd/A 23299-2025 artfynd.xlsx
+++ b/artfynd/A 23299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126270136</v>
       </c>
       <c r="B2" t="n">
-        <v>78997</v>
+        <v>79001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126270135</v>
       </c>
       <c r="B3" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126270161</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126270160</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23299-2025 artfynd.xlsx
+++ b/artfynd/A 23299-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>126270135</v>
       </c>
       <c r="B3" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23299-2025 artfynd.xlsx
+++ b/artfynd/A 23299-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126270136</v>
       </c>
       <c r="B2" t="n">
-        <v>79001</v>
+        <v>79004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126270135</v>
       </c>
       <c r="B3" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126270161</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126270160</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
